--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120464320</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mora kommun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>474236</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6784724</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121711375</v>
+        <v>121711714</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -932,19 +932,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474491</v>
+        <v>474512</v>
       </c>
       <c r="R4" t="n">
-        <v>6784752</v>
+        <v>6784780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121712009</v>
+        <v>121712245</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1054,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474435</v>
+        <v>474386</v>
       </c>
       <c r="R5" t="n">
-        <v>6784796</v>
+        <v>6784740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121712090</v>
+        <v>121712009</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1166,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474415</v>
+        <v>474435</v>
       </c>
       <c r="R6" t="n">
-        <v>6784797</v>
+        <v>6784796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121711685</v>
+        <v>121711375</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1281,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474499</v>
+        <v>474491</v>
       </c>
       <c r="R7" t="n">
-        <v>6784775</v>
+        <v>6784752</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121711342</v>
+        <v>121713810</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474487</v>
+        <v>474503</v>
       </c>
       <c r="R8" t="n">
-        <v>6784736</v>
+        <v>6784834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,19 +1423,9 @@
           <t>2024-12-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121711860</v>
+        <v>121711685</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1500,16 +1486,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474486</v>
+        <v>474499</v>
       </c>
       <c r="R9" t="n">
-        <v>6784836</v>
+        <v>6784775</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121711734</v>
+        <v>121712090</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1618,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474502</v>
+        <v>474415</v>
       </c>
       <c r="R10" t="n">
-        <v>6784825</v>
+        <v>6784797</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1653,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121711977</v>
+        <v>121711860</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1730,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474447</v>
+        <v>474486</v>
       </c>
       <c r="R11" t="n">
-        <v>6784801</v>
+        <v>6784836</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1765,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121713810</v>
+        <v>121711977</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,21 +1808,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474503</v>
+        <v>474447</v>
       </c>
       <c r="R12" t="n">
-        <v>6784834</v>
+        <v>6784801</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,9 +1865,19 @@
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,7 +1904,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121712245</v>
+        <v>121711342</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474386</v>
+        <v>474487</v>
       </c>
       <c r="R13" t="n">
-        <v>6784740</v>
+        <v>6784736</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121712488</v>
+        <v>121711528</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2050,19 +2050,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474290</v>
+        <v>474493</v>
       </c>
       <c r="R14" t="n">
-        <v>6784710</v>
+        <v>6784764</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,6 +2113,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121711528</v>
+        <v>121712425</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2162,19 +2166,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474493</v>
+        <v>474318</v>
       </c>
       <c r="R15" t="n">
-        <v>6784764</v>
+        <v>6784753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,7 +2226,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121712330</v>
+        <v>121711734</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474377</v>
+        <v>474502</v>
       </c>
       <c r="R16" t="n">
-        <v>6784785</v>
+        <v>6784825</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121712425</v>
+        <v>121712330</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474318</v>
+        <v>474377</v>
       </c>
       <c r="R17" t="n">
-        <v>6784753</v>
+        <v>6784785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121711714</v>
+        <v>121712488</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2508,13 +2508,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474512</v>
+        <v>474290</v>
       </c>
       <c r="R18" t="n">
-        <v>6784780</v>
+        <v>6784710</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,7 +2580,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121723263</v>
+        <v>121723362</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474210</v>
+        <v>474051</v>
       </c>
       <c r="R19" t="n">
-        <v>6784689</v>
+        <v>6784728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121724257</v>
+        <v>121723263</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,25 +2704,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474540</v>
+        <v>474210</v>
       </c>
       <c r="R20" t="n">
-        <v>6784812</v>
+        <v>6784689</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,7 +2804,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121724166</v>
+        <v>121724257</v>
       </c>
       <c r="B21" t="n">
         <v>90693</v>
@@ -2840,17 +2840,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björntjärnen, Dlr</t>
+          <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473935</v>
+        <v>474540</v>
       </c>
       <c r="R21" t="n">
-        <v>6784750</v>
+        <v>6784812</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121723362</v>
+        <v>121724166</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2928,41 +2928,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fryksås, Dlr</t>
+          <t>Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474051</v>
+        <v>473935</v>
       </c>
       <c r="R22" t="n">
-        <v>6784728</v>
+        <v>6784750</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,6 +3025,122 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121809878</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>474452</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6784753</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121711714</v>
+        <v>121711342</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474512</v>
+        <v>474487</v>
       </c>
       <c r="R4" t="n">
-        <v>6784780</v>
+        <v>6784736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121712245</v>
+        <v>121711977</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474386</v>
+        <v>474447</v>
       </c>
       <c r="R5" t="n">
-        <v>6784740</v>
+        <v>6784801</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121712009</v>
+        <v>121712245</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474435</v>
+        <v>474386</v>
       </c>
       <c r="R6" t="n">
-        <v>6784796</v>
+        <v>6784740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121711375</v>
+        <v>121712330</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1268,19 +1268,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474491</v>
+        <v>474377</v>
       </c>
       <c r="R7" t="n">
-        <v>6784752</v>
+        <v>6784785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1328,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121713810</v>
+        <v>121711528</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1362,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474503</v>
+        <v>474493</v>
       </c>
       <c r="R8" t="n">
-        <v>6784834</v>
+        <v>6784764</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,17 +1422,28 @@
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121711685</v>
+        <v>121711860</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1486,19 +1496,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474499</v>
+        <v>474486</v>
       </c>
       <c r="R9" t="n">
-        <v>6784775</v>
+        <v>6784836</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1556,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121712090</v>
+        <v>121711375</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1602,16 +1608,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474415</v>
+        <v>474491</v>
       </c>
       <c r="R10" t="n">
-        <v>6784797</v>
+        <v>6784752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1653,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,6 +1671,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121711860</v>
+        <v>121712009</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1720,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474486</v>
+        <v>474435</v>
       </c>
       <c r="R11" t="n">
-        <v>6784836</v>
+        <v>6784796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121711977</v>
+        <v>121712090</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1832,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474447</v>
+        <v>474415</v>
       </c>
       <c r="R12" t="n">
-        <v>6784801</v>
+        <v>6784797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121711342</v>
+        <v>121712488</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1944,13 +1954,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474487</v>
+        <v>474290</v>
       </c>
       <c r="R13" t="n">
-        <v>6784736</v>
+        <v>6784710</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2026,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121711528</v>
+        <v>121711685</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2059,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474493</v>
+        <v>474499</v>
       </c>
       <c r="R14" t="n">
-        <v>6784764</v>
+        <v>6784775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2356,7 +2366,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121712330</v>
+        <v>121711714</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2396,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474377</v>
+        <v>474512</v>
       </c>
       <c r="R17" t="n">
-        <v>6784785</v>
+        <v>6784780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121712488</v>
+        <v>121713810</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2508,13 +2518,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474290</v>
+        <v>474503</v>
       </c>
       <c r="R18" t="n">
-        <v>6784710</v>
+        <v>6784834</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2541,19 +2551,9 @@
           <t>2024-12-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121723263</v>
+        <v>121724257</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,25 +2704,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474210</v>
+        <v>474540</v>
       </c>
       <c r="R20" t="n">
-        <v>6784689</v>
+        <v>6784812</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121724257</v>
+        <v>121723263</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,25 +2816,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474540</v>
+        <v>474210</v>
       </c>
       <c r="R21" t="n">
-        <v>6784812</v>
+        <v>6784689</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121711342</v>
+        <v>121712245</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474487</v>
+        <v>474386</v>
       </c>
       <c r="R4" t="n">
-        <v>6784736</v>
+        <v>6784740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121711977</v>
+        <v>121711375</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1044,16 +1044,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474447</v>
+        <v>474491</v>
       </c>
       <c r="R5" t="n">
-        <v>6784801</v>
+        <v>6784752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,6 +1107,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121712245</v>
+        <v>121711714</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1162,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474386</v>
+        <v>474512</v>
       </c>
       <c r="R6" t="n">
-        <v>6784740</v>
+        <v>6784780</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121712330</v>
+        <v>121713810</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,21 +1254,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474377</v>
+        <v>474503</v>
       </c>
       <c r="R7" t="n">
-        <v>6784785</v>
+        <v>6784834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,19 +1311,9 @@
           <t>2024-12-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121711528</v>
+        <v>121712330</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1380,19 +1374,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474493</v>
+        <v>474377</v>
       </c>
       <c r="R8" t="n">
-        <v>6784764</v>
+        <v>6784785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,7 +1434,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1462,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121711860</v>
+        <v>121712090</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1502,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474486</v>
+        <v>474415</v>
       </c>
       <c r="R9" t="n">
-        <v>6784836</v>
+        <v>6784797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121711375</v>
+        <v>121711342</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1608,19 +1598,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474491</v>
+        <v>474487</v>
       </c>
       <c r="R10" t="n">
-        <v>6784752</v>
+        <v>6784736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1649,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,7 +1658,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,7 +1676,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121712009</v>
+        <v>121711977</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1730,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474435</v>
+        <v>474447</v>
       </c>
       <c r="R11" t="n">
-        <v>6784796</v>
+        <v>6784801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121712090</v>
+        <v>121711734</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1842,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474415</v>
+        <v>474502</v>
       </c>
       <c r="R12" t="n">
-        <v>6784797</v>
+        <v>6784825</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1900,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121712488</v>
+        <v>121711528</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1948,19 +1934,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474290</v>
+        <v>474493</v>
       </c>
       <c r="R13" t="n">
-        <v>6784710</v>
+        <v>6784764</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1978,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1988,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,6 +1997,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121711685</v>
+        <v>121712009</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2060,19 +2050,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474499</v>
+        <v>474435</v>
       </c>
       <c r="R14" t="n">
-        <v>6784775</v>
+        <v>6784796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,7 +2110,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2142,7 +2128,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121712425</v>
+        <v>121711685</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2176,16 +2162,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474318</v>
+        <v>474499</v>
       </c>
       <c r="R15" t="n">
-        <v>6784753</v>
+        <v>6784775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,6 +2225,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2254,7 +2244,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121711734</v>
+        <v>121711860</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2294,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474502</v>
+        <v>474486</v>
       </c>
       <c r="R16" t="n">
-        <v>6784825</v>
+        <v>6784836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121711714</v>
+        <v>121712488</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2406,13 +2396,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474512</v>
+        <v>474290</v>
       </c>
       <c r="R17" t="n">
-        <v>6784780</v>
+        <v>6784710</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121713810</v>
+        <v>121712425</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2484,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474503</v>
+        <v>474318</v>
       </c>
       <c r="R18" t="n">
-        <v>6784834</v>
+        <v>6784753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2551,9 +2541,19 @@
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121724257</v>
+        <v>121723263</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,25 +2704,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474540</v>
+        <v>474210</v>
       </c>
       <c r="R20" t="n">
-        <v>6784812</v>
+        <v>6784689</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121723263</v>
+        <v>121724166</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,41 +2816,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fryksås, Dlr</t>
+          <t>Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474210</v>
+        <v>473935</v>
       </c>
       <c r="R21" t="n">
-        <v>6784689</v>
+        <v>6784750</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121724166</v>
+        <v>121724257</v>
       </c>
       <c r="B22" t="n">
         <v>90693</v>
@@ -2952,17 +2952,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björntjärnen, Dlr</t>
+          <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473935</v>
+        <v>474540</v>
       </c>
       <c r="R22" t="n">
-        <v>6784750</v>
+        <v>6784812</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121712245</v>
+        <v>121712090</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474386</v>
+        <v>474415</v>
       </c>
       <c r="R4" t="n">
-        <v>6784740</v>
+        <v>6784797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121711375</v>
+        <v>121712425</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1044,19 +1044,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474491</v>
+        <v>474318</v>
       </c>
       <c r="R5" t="n">
-        <v>6784752</v>
+        <v>6784753</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121711714</v>
+        <v>121711528</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1160,16 +1156,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474512</v>
+        <v>474493</v>
       </c>
       <c r="R6" t="n">
-        <v>6784780</v>
+        <v>6784764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121712090</v>
+        <v>121712009</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474415</v>
+        <v>474435</v>
       </c>
       <c r="R9" t="n">
-        <v>6784797</v>
+        <v>6784796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121711342</v>
+        <v>121711375</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1598,16 +1598,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474487</v>
+        <v>474491</v>
       </c>
       <c r="R10" t="n">
-        <v>6784736</v>
+        <v>6784752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,6 +1661,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1676,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121711977</v>
+        <v>121712488</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1716,13 +1720,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474447</v>
+        <v>474290</v>
       </c>
       <c r="R11" t="n">
-        <v>6784801</v>
+        <v>6784710</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1765,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121711734</v>
+        <v>121711685</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1822,16 +1826,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474502</v>
+        <v>474499</v>
       </c>
       <c r="R12" t="n">
-        <v>6784825</v>
+        <v>6784775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,6 +1889,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121711528</v>
+        <v>121711342</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1934,19 +1942,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474493</v>
+        <v>474487</v>
       </c>
       <c r="R13" t="n">
-        <v>6784764</v>
+        <v>6784736</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1983,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1993,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,7 +2002,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2016,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121712009</v>
+        <v>121711734</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2056,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474435</v>
+        <v>474502</v>
       </c>
       <c r="R14" t="n">
-        <v>6784796</v>
+        <v>6784825</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121711685</v>
+        <v>121711714</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2162,19 +2166,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474499</v>
+        <v>474512</v>
       </c>
       <c r="R15" t="n">
-        <v>6784775</v>
+        <v>6784780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,7 +2226,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121712488</v>
+        <v>121711977</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474290</v>
+        <v>474447</v>
       </c>
       <c r="R17" t="n">
-        <v>6784710</v>
+        <v>6784801</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121712425</v>
+        <v>121712245</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474318</v>
+        <v>474386</v>
       </c>
       <c r="R18" t="n">
-        <v>6784753</v>
+        <v>6784740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121723263</v>
+        <v>121724257</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,25 +2704,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474210</v>
+        <v>474540</v>
       </c>
       <c r="R20" t="n">
-        <v>6784689</v>
+        <v>6784812</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121724166</v>
+        <v>121723263</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,41 +2816,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björntjärnen, Dlr</t>
+          <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473935</v>
+        <v>474210</v>
       </c>
       <c r="R21" t="n">
-        <v>6784750</v>
+        <v>6784689</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121724257</v>
+        <v>121724166</v>
       </c>
       <c r="B22" t="n">
         <v>90693</v>
@@ -2952,17 +2952,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fryksås, Dlr</t>
+          <t>Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474540</v>
+        <v>473935</v>
       </c>
       <c r="R22" t="n">
-        <v>6784812</v>
+        <v>6784750</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121712090</v>
+        <v>121713810</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474415</v>
+        <v>474503</v>
       </c>
       <c r="R4" t="n">
-        <v>6784797</v>
+        <v>6784834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,19 +971,9 @@
           <t>2024-12-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121712425</v>
+        <v>121712245</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1050,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474318</v>
+        <v>474386</v>
       </c>
       <c r="R5" t="n">
-        <v>6784753</v>
+        <v>6784740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121711528</v>
+        <v>121711734</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1156,19 +1146,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474493</v>
+        <v>474502</v>
       </c>
       <c r="R6" t="n">
-        <v>6784764</v>
+        <v>6784825</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,7 +1206,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121713810</v>
+        <v>121712090</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474503</v>
+        <v>474415</v>
       </c>
       <c r="R7" t="n">
-        <v>6784834</v>
+        <v>6784797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,9 +1297,19 @@
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121712330</v>
+        <v>121711685</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1374,16 +1370,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474377</v>
+        <v>474499</v>
       </c>
       <c r="R8" t="n">
-        <v>6784785</v>
+        <v>6784775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121712009</v>
+        <v>121711714</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474435</v>
+        <v>474512</v>
       </c>
       <c r="R9" t="n">
-        <v>6784796</v>
+        <v>6784780</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121711375</v>
+        <v>121712330</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1598,19 +1598,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474491</v>
+        <v>474377</v>
       </c>
       <c r="R10" t="n">
-        <v>6784752</v>
+        <v>6784785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1649,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,7 +1658,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,7 +1676,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121712488</v>
+        <v>121711860</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1720,13 +1716,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474290</v>
+        <v>474486</v>
       </c>
       <c r="R11" t="n">
-        <v>6784710</v>
+        <v>6784836</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121711685</v>
+        <v>121712488</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1826,22 +1822,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474499</v>
+        <v>474290</v>
       </c>
       <c r="R12" t="n">
-        <v>6784775</v>
+        <v>6784710</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,7 +1882,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1908,7 +1900,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121711342</v>
+        <v>121712425</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1948,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474487</v>
+        <v>474318</v>
       </c>
       <c r="R13" t="n">
-        <v>6784736</v>
+        <v>6784753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1993,7 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2012,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121711734</v>
+        <v>121711977</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2060,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474502</v>
+        <v>474447</v>
       </c>
       <c r="R14" t="n">
-        <v>6784825</v>
+        <v>6784801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121711714</v>
+        <v>121711375</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2166,16 +2158,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474512</v>
+        <v>474491</v>
       </c>
       <c r="R15" t="n">
-        <v>6784780</v>
+        <v>6784752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,7 +2202,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2212,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,6 +2221,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2244,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121711860</v>
+        <v>121711342</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2284,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474486</v>
+        <v>474487</v>
       </c>
       <c r="R16" t="n">
-        <v>6784836</v>
+        <v>6784736</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,7 +2315,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2325,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121711977</v>
+        <v>121712009</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2396,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474447</v>
+        <v>474435</v>
       </c>
       <c r="R17" t="n">
-        <v>6784801</v>
+        <v>6784796</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121712245</v>
+        <v>121711528</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2502,16 +2498,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474386</v>
+        <v>474493</v>
       </c>
       <c r="R18" t="n">
-        <v>6784740</v>
+        <v>6784764</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,6 +2561,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121723362</v>
+        <v>121724257</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,25 +2592,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474051</v>
+        <v>474540</v>
       </c>
       <c r="R19" t="n">
-        <v>6784728</v>
+        <v>6784812</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121724257</v>
+        <v>121723362</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,25 +2704,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474540</v>
+        <v>474051</v>
       </c>
       <c r="R20" t="n">
-        <v>6784812</v>
+        <v>6784728</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121712245</v>
+        <v>121711714</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474386</v>
+        <v>474512</v>
       </c>
       <c r="R5" t="n">
-        <v>6784740</v>
+        <v>6784780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121711734</v>
+        <v>121712330</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474502</v>
+        <v>474377</v>
       </c>
       <c r="R6" t="n">
-        <v>6784825</v>
+        <v>6784785</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121712090</v>
+        <v>121711734</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474415</v>
+        <v>474502</v>
       </c>
       <c r="R7" t="n">
-        <v>6784797</v>
+        <v>6784825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,7 +1336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121711685</v>
+        <v>121711977</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1370,19 +1370,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474499</v>
+        <v>474447</v>
       </c>
       <c r="R8" t="n">
-        <v>6784775</v>
+        <v>6784801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,7 +1430,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121711714</v>
+        <v>121711860</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1492,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474512</v>
+        <v>474486</v>
       </c>
       <c r="R9" t="n">
-        <v>6784780</v>
+        <v>6784836</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121712330</v>
+        <v>121711342</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1604,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474377</v>
+        <v>474487</v>
       </c>
       <c r="R10" t="n">
-        <v>6784785</v>
+        <v>6784736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,7 +1672,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121711860</v>
+        <v>121711375</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1710,16 +1706,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474486</v>
+        <v>474491</v>
       </c>
       <c r="R11" t="n">
-        <v>6784836</v>
+        <v>6784752</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1760,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,6 +1769,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121712488</v>
+        <v>121712090</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474290</v>
+        <v>474415</v>
       </c>
       <c r="R12" t="n">
-        <v>6784710</v>
+        <v>6784797</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,7 +1900,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121712425</v>
+        <v>121712245</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474318</v>
+        <v>474386</v>
       </c>
       <c r="R13" t="n">
-        <v>6784753</v>
+        <v>6784740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121711977</v>
+        <v>121711528</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2046,16 +2046,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474447</v>
+        <v>474493</v>
       </c>
       <c r="R14" t="n">
-        <v>6784801</v>
+        <v>6784764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,6 +2109,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2128,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121711375</v>
+        <v>121712488</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2158,22 +2162,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474491</v>
+        <v>474290</v>
       </c>
       <c r="R15" t="n">
-        <v>6784752</v>
+        <v>6784710</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,7 +2203,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2212,7 +2213,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,7 +2222,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121711342</v>
+        <v>121712009</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474487</v>
+        <v>474435</v>
       </c>
       <c r="R16" t="n">
-        <v>6784736</v>
+        <v>6784796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121712009</v>
+        <v>121712425</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474435</v>
+        <v>474318</v>
       </c>
       <c r="R17" t="n">
-        <v>6784796</v>
+        <v>6784753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121711528</v>
+        <v>121711685</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474493</v>
+        <v>474499</v>
       </c>
       <c r="R18" t="n">
-        <v>6784764</v>
+        <v>6784775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121724257</v>
+        <v>121723263</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,25 +2592,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474540</v>
+        <v>474210</v>
       </c>
       <c r="R19" t="n">
-        <v>6784812</v>
+        <v>6784689</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121723263</v>
+        <v>121724166</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,41 +2816,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fryksås, Dlr</t>
+          <t>Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474210</v>
+        <v>473935</v>
       </c>
       <c r="R21" t="n">
-        <v>6784689</v>
+        <v>6784750</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121724166</v>
+        <v>121724257</v>
       </c>
       <c r="B22" t="n">
         <v>90693</v>
@@ -2952,17 +2952,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björntjärnen, Dlr</t>
+          <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473935</v>
+        <v>474540</v>
       </c>
       <c r="R22" t="n">
-        <v>6784750</v>
+        <v>6784812</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 43588-2024 artfynd.xlsx
+++ b/artfynd/A 43588-2024 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121713810</v>
+        <v>121712488</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>78629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474503</v>
+        <v>474290</v>
       </c>
       <c r="R4" t="n">
-        <v>6784834</v>
+        <v>6784710</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,9 +971,19 @@
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121711714</v>
+        <v>121712009</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474512</v>
+        <v>474435</v>
       </c>
       <c r="R5" t="n">
-        <v>6784780</v>
+        <v>6784796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121712330</v>
+        <v>121712245</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474377</v>
+        <v>474386</v>
       </c>
       <c r="R6" t="n">
-        <v>6784785</v>
+        <v>6784740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121711734</v>
+        <v>121711714</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474502</v>
+        <v>474512</v>
       </c>
       <c r="R7" t="n">
-        <v>6784825</v>
+        <v>6784780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121711977</v>
+        <v>121711528</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,16 +1380,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474447</v>
+        <v>474493</v>
       </c>
       <c r="R8" t="n">
-        <v>6784801</v>
+        <v>6784764</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,6 +1443,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1451,7 +1465,7 @@
         <v>121711860</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121711342</v>
+        <v>121711977</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474487</v>
+        <v>474447</v>
       </c>
       <c r="R10" t="n">
-        <v>6784736</v>
+        <v>6784801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121711375</v>
+        <v>121713810</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>90760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,37 +1702,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474491</v>
+        <v>474503</v>
       </c>
       <c r="R11" t="n">
-        <v>6784752</v>
+        <v>6784834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,28 +1759,17 @@
           <t>2024-12-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121712090</v>
+        <v>121711734</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474415</v>
+        <v>474502</v>
       </c>
       <c r="R12" t="n">
-        <v>6784797</v>
+        <v>6784825</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121712245</v>
+        <v>121711342</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474386</v>
+        <v>474487</v>
       </c>
       <c r="R13" t="n">
-        <v>6784740</v>
+        <v>6784736</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121711528</v>
+        <v>121712330</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,19 +2046,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474493</v>
+        <v>474377</v>
       </c>
       <c r="R14" t="n">
-        <v>6784764</v>
+        <v>6784785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2128,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121712488</v>
+        <v>121712425</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474290</v>
+        <v>474318</v>
       </c>
       <c r="R15" t="n">
-        <v>6784710</v>
+        <v>6784753</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2203,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2213,7 +2209,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121712009</v>
+        <v>121711685</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,16 +2270,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474435</v>
+        <v>474499</v>
       </c>
       <c r="R16" t="n">
-        <v>6784796</v>
+        <v>6784775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2325,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,6 +2333,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121712425</v>
+        <v>121711375</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,16 +2386,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474318</v>
+        <v>474491</v>
       </c>
       <c r="R17" t="n">
-        <v>6784753</v>
+        <v>6784752</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,6 +2449,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2464,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121711685</v>
+        <v>121712090</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,19 +2502,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474499</v>
+        <v>474415</v>
       </c>
       <c r="R18" t="n">
-        <v>6784775</v>
+        <v>6784797</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2561,7 +2562,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>121723263</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>121723362</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121724166</v>
+        <v>121724257</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2840,17 +2840,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björntjärnen, Dlr</t>
+          <t>Fryksås, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473935</v>
+        <v>474540</v>
       </c>
       <c r="R21" t="n">
-        <v>6784750</v>
+        <v>6784812</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121724257</v>
+        <v>121724166</v>
       </c>
       <c r="B22" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2952,17 +2952,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fryksås, Dlr</t>
+          <t>Björntjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474540</v>
+        <v>473935</v>
       </c>
       <c r="R22" t="n">
-        <v>6784812</v>
+        <v>6784750</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,7 +3031,7 @@
         <v>121809878</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
